--- a/incoming/WGR_Store_Data.xlsx
+++ b/incoming/WGR_Store_Data.xlsx
@@ -799,12 +799,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Northeast Wisconsin's #1 furniture &amp; mattress retailer since 1946</t>
+          <t>Serving Northeast Wisconsin since 1946 — proudly employee-owned</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EST. 1946 - EMPLOYEE-OWNED - WISCONSIN</t>
+          <t>EST. 1946 · EMPLOYEE-OWNED · NORTHEAST WISCONSIN</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -846,27 +846,27 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>WG&amp;R Sleep Shop</t>
+          <t>WG&amp;R Sleep Consultation</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Let's find your</t>
+          <t>Let's find the mattress</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>best night's sleep</t>
+          <t>made for how you sleep</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer a few quick questions and we'll match you to the right mattress - backed by our </t>
+          <t xml:space="preserve">Answer a few questions and our sleep specialists will match you to the right mattress — proudly </t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>125-Night Sleep Guarantee</t>
+          <t>employee-owned in Northeast Wisconsin since 1946</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Start the Sleep Quiz</t>
+          <t>Start My Sleep Consultation</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Takes about 2 minutes</t>
+          <t>About 2 minutes, no pressure</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>

--- a/incoming/WGR_Store_Data.xlsx
+++ b/incoming/WGR_Store_Data.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>en,es</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,62 +1193,102 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>differentiator1Title</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>differentiator1Detail</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>differentiator2Title</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>differentiator2Detail</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>displayBadges (ES)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>highlight (ES)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>reason_cooling (ES)</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>reason_pressureRelief (ES)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>reason_motionIsolation (ES)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>reason_support (ES)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>reason_plush (ES)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>reason_medium (ES)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>reason_firm (ES)</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>reason_durability (ES)</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>reason_default (ES)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>topPickReason (ES)</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>differentiator1Title (ES)</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>differentiator1Detail (ES)</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>differentiator2Title (ES)</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>differentiator2Detail (ES)</t>
         </is>
       </c>
     </row>
@@ -1339,14 +1379,86 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Espuma viscoelástica|Alivio de presión|Medio</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Se adapta a tu cuerpo para un alivio profundo de presión</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Espuma viscoelástica que se adapta al cuerpo para un alivio profundo de presión.</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>El material TEMPUR se adapta a ti para aliviar la presión y reducir la transferencia de movimiento.</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Contorno TEMPUR de adaptación lenta</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Se ajusta de cerca al cuerpo en vez de empujar como una cama con más rebote.</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Sensación de espuma que absorbe movimiento</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Mantiene más silencioso el movimiento de la pareja que los diseños con resortes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1435,14 +1547,86 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Enfriamiento|Híbrido|Medio</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Confort adaptable con soporte híbrido y frescura toda la noche</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Confort de espuma adaptable con respuesta híbrida y frescura toda la noche.</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Duerme más fresco con confort TEMPUR y soporte híbrido sensible.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Contorno TEMPUR con elevación de resortes</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Combina alivio de presión lento arriba con movimiento más fácil gracias a la base híbrida.</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Enfriamiento enfocado Breeze</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Diseñado para sentirse más fresco que la espuma tradicional de contorno profundo.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1531,14 +1715,86 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Enfriamiento|Firme|Alivio de presión</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Nuestro TEMPUR más fresco firme y con buen soporte</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Nuestra opción más fresca con confort firme y soporte completo.</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Nuestro TEMPUR más fresco con confort firme y soporte durante toda la noche.</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>La sensación Breeze más firme</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Una superficie estable de 7/10 ofrece menos hundimiento sin perder el contorno TEMPUR.</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Máximo enfriamiento Breeze</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>La construcción enfocada en frescura es el principal avance dentro de la línea Breeze.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1627,14 +1883,86 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Firme|Soporte de resortes|Duradero</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Soporte firme de resortes hecho a mano y diseñado para durar</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Soporte firme y duradero de resortes hecho a mano para brindar confort prolongado.</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Los resortes de precisión brindan soporte firme y duradero.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Respuesta de resortes hecha a mano</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Los resortes de precisión crean una sensación estructurada con más elevación que la espuma.</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Enfoque firme y duradero</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Diseñado para conservar una sensación estable en vez de un hundimiento profundo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1723,14 +2051,86 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Resortes de lujo|Medio|Duradero</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Lujo artesanal suave en la superficie y apoyado por debajo</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Resortes y espumas premium equilibrados para un lujo suave y con buen soporte.</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Resortes y espumas premium hechos a mano para un lujo equilibrado y duradero.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Equilibrio de lujo suave y apoyado</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Las capas de confort suavizan el primer contacto mientras los resortes mantienen el apoyo.</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Construcción estilo reliquia</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Espumas y resortes premium crean una sensación sustancial y una construcción duradera.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1819,14 +2219,86 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Látex Talalay|Suave|Duradero</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Confort suave de látex completo con durabilidad excepcional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Suavidad de látex Talalay natural con durabilidad excepcional.</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Confort suave de látex completo con una garantía que destaca.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Flotación de látex Talalay</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Se siente elástico y responde al instante sin el hundimiento lento de la espuma viscoelástica.</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Durabilidad de látex completo</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Usa látex resistente en toda la estructura de confort y no solo como una capa delgada.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1915,14 +2387,86 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Rejilla GelFlex|Enfriamiento|Sensible</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Rejilla GelFlex premium fresca sensible y sin presión</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>La rejilla GelFlex premium de Purple ofrece una sensación fresca y sensible con alivio de presión.</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>La rejilla premium de Purple brinda una sensación fresca y sensible sin presión.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Respuesta de rejilla GelFlex</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>La rejilla cede justo bajo los puntos de presión y mantiene apoyo alrededor.</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Sensación flotante y abierta</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Envuelve menos que la espuma y permite moverse con mayor facilidad.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2011,14 +2555,86 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Resortes embolsados|Medio|Aislamiento de movimiento</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Sensación media de lujo con soporte premium de resortes</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Confort medio de lujo sobre soporte premium de resortes embolsados.</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Sensación media de lujo sobre el soporte premium de resortes embolsados Beautyrest.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Centro premium de resortes embolsados</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Los resortes individuales dan apoyo definido y limitan el movimiento a través de la cama.</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Acolchado medio de lujo</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Agrega una superficie más refinada sin perder la respuesta de los resortes.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2107,14 +2723,86 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Ajuste inteligente|Firmeza doble|Zonas</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Firmeza inteligente ajustable por lado a tu manera</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Una cama inteligente que ajusta la firmeza de cada lado a cada persona.</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Ajusta la firmeza de cada lado con soporte inteligente controlado por aplicación.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Firmeza independiente por lado</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Cada persona puede ajustar su lado sin comprometerse con una sola sensación compartida.</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Ajuste controlado por aplicación</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>La firmeza puede cambiar después de la compra cuando evolucionen las preferencias.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2199,14 +2887,86 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Rejilla GelFlex|Enfriamiento|Sensible</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>La rejilla Purple original fresca sensible y adaptable</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>La rejilla Purple original ofrece frescura respuesta y adaptación.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Confort fresco y sensible de rejilla que se adapta mientras te mueves.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Experiencia GelFlex original</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>La rejilla se dobla bajo los puntos de presión y recupera su forma al moverte.</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Perfil Purple más sencillo</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Ofrece la sensación flotante de la rejilla sin una construcción de lujo más gruesa.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2295,14 +3055,86 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Híbrido de rejilla|Firme|Sensible</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Rejilla firme sobre resortes con flujo de aire</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Soporte firme de rejilla sobre resortes con ventilación y alivio de presión.</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Soporte firme de rejilla sobre resortes con ventilación y alivio de presión.</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Rejilla firme sobre resortes</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Combina la superficie flexible de Purple con el empuje más fuerte de una base híbrida.</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Apoyo ventilado y sensible</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>La rejilla abierta y los resortes se sienten menos encerrados que una espuma firme y densa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2391,14 +3223,86 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Enfriamiento|Zonas|Híbrido</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Duerme más fresco con soporte por zonas</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Duerme más fresco con soporte por zonas pensado para quienes sienten calor.</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Duerme más fresco con soporte por zonas para quienes sienten calor.</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Híbrido enfocado en enfriamiento</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Su propósito principal es reducir el calor sin perder una sensación fácil para moverse.</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Distribución de apoyo por zonas</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>Diferentes áreas amortiguan los puntos de presión y estabilizan el centro del cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2487,14 +3391,86 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Híbrido|Enfriamiento|Medio</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Confort híbrido equilibrado con frescura</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Confort híbrido equilibrado y fresco a un precio accesible.</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Confort híbrido equilibrado y fresco a un precio accesible.</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Híbrido equilibrado para diario</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>No envuelve demasiado ni se siente muy firme; busca una sensación intermedia fácil.</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Elevación de resortes accesible</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>Ofrece el movimiento de un híbrido sin subir a una construcción premium.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2583,14 +3559,86 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Híbrido|Medio|Soporte</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Confort híbrido Sealy confiable</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Soporte híbrido Sealy confiable para un confort diario equilibrado.</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Híbrido Sealy confiable ajustado para un confort equilibrado toda la noche.</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Sensación híbrida Sealy familiar</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Una superficie media sobre apoyo sensible se entiende rápidamente al probarla.</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Simplicidad enfocada en apoyo</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>Prioriza alineación y movimiento confiables sobre tecnología inteligente o de rejilla.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2679,14 +3727,86 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Híbrido|Firme|Soporte</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Soporte híbrido firme para mantener la alineación</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Soporte híbrido firme que ayuda a mantener la columna alineada.</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Soporte híbrido firme que ayuda a mantener la columna alineada.</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Perfil Posturepedic firme</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Una superficie de 7/10 mantiene el cuerpo más encima del colchón que dentro de él.</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Construcción híbrida estable</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Combina capas firmes con resortes para una respuesta más estable que la espuma firme sola.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2775,14 +3895,86 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Resortes embolsados|Firme|Aislamiento de movimiento</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Soporte firme de resortes con sensación de lujo</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Soporte firme de resortes embolsados con una verdadera sensación de lujo.</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Soporte firme de resortes embolsados Beautyrest con sensación de lujo.</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Sensación firme de resortes Beautyrest</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Ofrece un empuje fuerte con la respuesta familiar de resortes premium.</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Control de movimiento embolsado</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Los resortes individuales se mueven con más independencia que una unidad tradicional conectada.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2867,14 +4059,86 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Hecho en Wisconsin|Suave|Alivio de presión</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Confort suave hecho a mano en Wisconsin</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Confort suave que alivia la presión y está hecho a mano en Wisconsin.</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Confort suave Astor Park que alivia la presión y está hecho a mano en Wisconsin.</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Suavidad hecha a mano en Wisconsin</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Fabricado localmente con una superficie muy suave de 3/10 para quien quiere acolchado inmediato.</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Mayor alivio en puntos de presión</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>Permite que hombros y caderas bajen más que en las opciones medias y firmes.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2959,14 +4223,86 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Hecho en Wisconsin|Firme|Duradero</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Soporte firme hecho a mano en Wisconsin</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Confort firme y con buen soporte hecho a mano en Wisconsin.</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Firmeza artesanal de Wisconsin con soporte confiable toda la noche.</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Firmeza hecha a mano en Wisconsin</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Fabricado localmente con una superficie estable de 7/10 y poco hundimiento inicial.</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Apoyo enfocado en durabilidad</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>Destaca una construcción firme y directa sobre capas adicionales de suavidad.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3055,14 +4391,86 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Híbrido|Enfriamiento|Aislamiento de movimiento</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Confort híbrido fresco para parejas</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Confort híbrido fresco con buen aislamiento de movimiento para parejas.</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Confort híbrido fresco y aislamiento de movimiento para parejas.</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Híbrido fresco para parejas</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Combina ventilación y control de movimiento para parejas que duermen con calor o se despiertan.</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Equilibrio de espuma y resortes</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>Ofrece algo de contorno arriba y conserva el movimiento más fácil de un híbrido.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3151,14 +4559,86 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Espuma viscoelástica|Enfriamiento|Medio</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Confort fresco de espuma a un precio accesible</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Confort fresco de espuma en caja que cuida el presupuesto.</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>Confort fresco de espuma en caja que cuida el presupuesto.</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>Inicio sencillo de espuma</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Ofrece contorno cercano y una superficie silenciosa sin el rebote de resortes.</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Enfriamiento con buen valor</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>Agrega materiales para controlar el calor dentro del nivel más accesible.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3247,14 +4727,86 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Híbrido|Enfriamiento|Medio</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Respuesta híbrida fresca a precio inicial</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Respuesta híbrida y frescura a un precio inicial accesible.</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Respuesta híbrida y frescura a un precio inicial accesible.</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>Elevación híbrida de entrada</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Los resortes facilitan girarse y levantarse más que en el Classic de espuma.</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Frescura a precio inicial</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>Combina una superficie más fresca con apoyo híbrido en el nivel de entrada.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3343,14 +4895,86 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Híbrido|Medio firme|Buen valor</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Híbrido suave y firme con sensación superior a su precio</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Un híbrido suave y firme que se siente superior a su precio.</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Un híbrido suave y firme que se siente muy superior a su precio.</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Contraste suave y firme</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>El acolchado suaviza la parte superior mientras la base híbrida de 6/10 mantiene empuje.</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Sensación de valor más sustancial</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>Busca una impresión más sólida y terminada que un colchón inicial básico.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3435,14 +5059,86 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Suave|Acolchado|Buen valor</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Confort suave y confiable a un precio accesible</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Confort suave y accesible de una marca reconocida.</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Confort suave y accesible de una marca conocida.</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>Sensación Sealy suave de entrada</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Una superficie de 3/10 da suavidad inmediata sin la complejidad del nivel premium.</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Alivio de presión sencillo</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>Usa acolchado suave y directo para hombros y caderas a un precio accesible.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3527,14 +5223,86 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Hecho en Wisconsin|Firme|Buen valor</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Soporte firme hecho en Wisconsin a un gran valor</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Soporte firme hecho en Wisconsin a un precio accesible.</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Soporte firme hecho en Wisconsin a un precio ideal para una habitación de visitas.</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>Valor firme hecho en Wisconsin</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Fabricado localmente con una sensación estable de 7/10 y una propuesta de apoyo directa.</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Simplicidad para habitación de visitas</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>Prioriza firmeza confiable y precio sobre capas de enfriamiento o lujo.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3623,14 +5391,86 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Euro Top|Medio|Buen valor</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Euro top suave sobre soporte confiable</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Confort suave de euro top sobre soporte confiable de resortes.</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Confort suave de euro top sobre soporte confiable de resortes.</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Primera impresión Euro Top</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>El acolchado cosido crea una superficie más suave sobre un centro de apoyo medio.</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Respuesta tradicional de resortes</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>Se siente más familiar y elástico que un colchón de espuma de contorno lento.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3719,14 +5559,86 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Híbrido|Medio|Buen valor</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Confort híbrido mejorado con más espuma y soporte</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Los materiales transpirables ayudan a disipar el calor.</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>La superficie amortigua hombros y caderas para aliviar puntos de presión.</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Ayuda a reducir la transferencia de movimiento entre ambos lados de la cama.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>El sistema de soporte ayuda a mantener el cuerpo alineado.</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>La superficie suave ofrece mayor acolchado y adaptación.</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>La sensación media equilibra suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>La superficie firme ofrece apoyo estable con menos hundimiento.</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Los materiales resistentes están diseñados para conservar su sensación.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Más espuma y soporte que el híbrido de entrada.</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>Más espuma y soporte que el híbrido de entrada para ofrecer un poco más.</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Confort híbrido mejorado</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>Agrega más acolchado y apoyo que el híbrido DreamCloud de entrada.</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Respuesta intermedia</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>Mantiene una sensación media con elevación de resortes sin hundimiento profundo ni empuje firme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3739,7 +5651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3825,25 +5737,30 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>Score: Reflux</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>Score: Premium</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Score: Position Side</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Score: Position Back</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score: Position Stomach</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Score: Allergies</t>
         </is>
@@ -3860,13 +5777,21 @@
           <t>BedTech Relax Lifestyle Base</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Base Ajustable BedTech Relax Lifestyle</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>adjustable</t>
@@ -3880,7 +5805,11 @@
           <t>Adjustable power base with head &amp; foot articulation, wireless remote, and memory positions.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Base eléctrica ajustable con elevación de cabeza y pies, control inalámbrico y posiciones de memoria.</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>images/accessories/base-bedtech-relax.jpg</t>
@@ -3901,12 +5830,15 @@
         <v>4</v>
       </c>
       <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3919,13 +5851,21 @@
           <t>TEMPUR-Ergo Smart 3.0 Base</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Base TEMPUR-Ergo Smart 3.0</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>adjustable</t>
@@ -3939,7 +5879,11 @@
           <t>Smart adjustable base with app control, head &amp; foot adjustment, and sleep tracking.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Base inteligente ajustable con control por aplicación, elevación de cabeza y pies, y seguimiento del sueño.</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>images/accessories/base-tempur-ergo-smart.jpg</t>
@@ -3960,12 +5904,15 @@
         <v>4</v>
       </c>
       <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3978,13 +5925,21 @@
           <t>Purple Premium Plus Smart Base</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Base Inteligente Purple Premium Plus</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>adjustable</t>
@@ -3998,7 +5953,11 @@
           <t>Smart adjustable base with app control and full head &amp; foot articulation.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Base inteligente ajustable con control por aplicación y articulación completa de cabeza y pies.</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>images/accessories/base-purple-premium-plus.jpg</t>
@@ -4019,12 +5978,15 @@
         <v>4</v>
       </c>
       <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4037,13 +5999,21 @@
           <t>WG&amp;R Factory Direct Slate Foundation</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Base Slate de WG&amp;R Factory Direct</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>foundation</t>
@@ -4057,7 +6027,11 @@
           <t>Sturdy standard-height foundation - solid platform support for any mattress.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Base resistente de altura estándar con soporte de plataforma sólida para cualquier colchón.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>images/accessories/foundation-wgr-slate.jpg</t>
@@ -4080,6 +6054,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4092,13 +6067,21 @@
           <t>WG&amp;R Slate Low-Profile Foundation</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Base Slate de Perfil Bajo de WG&amp;R</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>low_profile</t>
@@ -4112,7 +6095,11 @@
           <t>Reduced-height foundation - ideal for taller mattresses or a low-profile look.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Base de menor altura, ideal para colchones altos o para lograr una apariencia de perfil bajo.</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>images/accessories/foundation-wgr-slate-lowpro.jpg</t>
@@ -4135,6 +6122,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4147,13 +6135,21 @@
           <t>WG&amp;R Factory Direct Bunkie Board</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tabla Bunkie de WG&amp;R Factory Direct</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Foundations &amp; Support</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bases y Soportes</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>bunkie</t>
@@ -4167,7 +6163,11 @@
           <t>Slim 2-inch support board for platform and bunk beds.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tabla delgada de soporte de 2 pulgadas para camas de plataforma y literas.</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>images/accessories/bunkie-wgr.jpg</t>
@@ -4190,6 +6190,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4202,13 +6203,21 @@
           <t>TEMPUR-Breeze ProLo 2.0 Pillow</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Almohada TEMPUR-Breeze ProLo 2.0</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Pillows</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Almohadas</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>225</v>
@@ -4218,7 +6227,11 @@
           <t>Cooling low-profile TEMPUR pillow for back and stomach sleepers.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Almohada TEMPUR fresca de perfil bajo para quienes duermen boca arriba o boca abajo.</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>images/accessories/pillow-tempur-breeze-prolo.jpg</t>
@@ -4240,13 +6253,14 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4259,13 +6273,21 @@
           <t>TEMPUR-Adapt ProAdjust Pillow</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Almohada TEMPUR-Adapt ProAdjust</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Pillows</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Almohadas</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>125</v>
@@ -4275,7 +6297,11 @@
           <t>Adjustable-fill TEMPUR pillow that customizes to any sleep position.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Almohada TEMPUR de relleno ajustable que se adapta a cualquier posición para dormir.</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>images/accessories/pillow-tempur-proadjust.jpg</t>
@@ -4294,16 +6320,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4316,13 +6343,21 @@
           <t>Healthy Sleep Cool-Tech Graphite Pillow</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Almohada Healthy Sleep Cool-Tech Graphite</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Pillows</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Almohadas</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>109</v>
@@ -4332,7 +6367,11 @@
           <t>Graphite-infused cooling pillow that draws heat away all night.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Almohada fresca con grafito que ayuda a disipar el calor durante toda la noche.</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>images/accessories/pillow-cooltech-graphite.jpg</t>
@@ -4353,14 +6392,15 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4373,13 +6413,21 @@
           <t>Purple Waterproof Protector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Protector Impermeable Purple</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Protectors</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Protectores</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>119</v>
@@ -4389,7 +6437,11 @@
           <t>Waterproof protector that guards your mattress while staying breathable.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Protector impermeable y transpirable que ayuda a cuidar el colchón.</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>images/accessories/protector-purple-waterproof.jpg</t>
@@ -4397,7 +6449,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>all, allergies</t>
+          <t>all, allergies, spills, everyday</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4411,7 +6463,8 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4426,13 +6479,21 @@
           <t>Healthy Sleep Premium Encasement</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Funda Integral Healthy Sleep Premium</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Protectors</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Protectores</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>79</v>
@@ -4442,7 +6503,11 @@
           <t>Full-zip encasement - allergen and dust-mite barrier on all six sides.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Funda integral con cierre que crea una barrera contra alérgenos y ácaros en los seis lados.</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>images/accessories/protector-healthy-sleep-encasement.jpg</t>
@@ -4450,7 +6515,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>allergies, all</t>
+          <t>allergies, all, everyday</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -4464,7 +6529,8 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4479,13 +6545,21 @@
           <t>TEMPUR-Protect Breeze Protector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Protector TEMPUR-Protect Breeze</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Protectors</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Protectores</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>249</v>
@@ -4495,7 +6569,11 @@
           <t>Cooling protector that adds a breathable layer of protection.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Protector fresco que agrega una capa transpirable de protección.</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>images/accessories/protector-tempur-breeze.jpg</t>
@@ -4503,7 +6581,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>cooling, hot_sleeper, all</t>
+          <t>cooling, hot_sleeper, all, everyday</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -4520,6 +6598,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/incoming/WGR_Store_Data.xlsx
+++ b/incoming/WGR_Store_Data.xlsx
@@ -833,17 +833,49 @@
           <t>Northeast Wisconsin</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>DreamFinder - Cuestionario del Sueño de WG&amp;R Furniture</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Responde el cuestionario de WG&amp;R Sleep Shop y recibe recomendaciones personalizadas de colchones.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>DreamFinder - WG&amp;R Furniture</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sirviendo a Northeast Wisconsin desde 1946 — con orgullo, propiedad de sus empleados</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>PROPIEDAD DE SUS EMPLEADOS · NORTHEAST WISCONSIN · DESDE 1946</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Solo usaremos tu correo para enviarte tus resultados.</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>En stock en WG&amp;R</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Northeast Wisconsin</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>WG&amp;R Sleep Consultation</t>
@@ -884,14 +916,38 @@
           <t>About 2 minutes, no pressure</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>PROPIEDAD DE SUS EMPLEADOS · NORTHEAST WISCONSIN · DESDE 1946</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Northeast Wisconsin,</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>tu tienda del descanso.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Responde unas preguntas y revisa tus opciones de colchón con un especialista del descanso de WG&amp;R.</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Encontrar Mi Opción Ideal</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Aproximadamente 2 minutos · Sin presión</t>
+        </is>
+      </c>
       <c r="BA2" t="inlineStr">
         <is>
           <t>DreamFinder - WG&amp;R Furniture</t>

--- a/incoming/WGR_Store_Data.xlsx
+++ b/incoming/WGR_Store_Data.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG2"/>
+  <dimension ref="A1:CK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,35 +684,185 @@
       </c>
       <c r="BA1" t="inlineStr">
         <is>
+          <t>Discount Mode</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Discount Percentage</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Discount Validity Days</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Discount Scope</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Discount Scope (ES)</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Discount Landing Hint</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Discount Landing Hint (ES)</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Discount Demo Delivery Note</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Discount Demo Delivery Note (ES)</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Discount Terms</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Discount Terms (ES)</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Privacy Draft Notice</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Privacy Heading</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Privacy Body</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Disclaimer Heading</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Disclaimer Body</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Ownership Badge</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Locations Label</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Locations</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Privacy Draft Notice (ES)</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Privacy Heading (ES)</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Privacy Body (ES)</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Disclaimer Heading (ES)</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>Disclaimer Body (ES)</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>Voice Retailer Subline</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Voice Outcome Label</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Voice Outcome Items</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Voice Retailer Subline (ES)</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Voice Outcome Label (ES)</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Voice Outcome Items (ES)</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
           <t>Manifest Name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Manifest Short Name</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>Manifest Description</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Manifest Start URL</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>Manifest Theme Color</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Manifest Background Color</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>App Icon File</t>
         </is>
@@ -804,7 +955,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EST. 1946 · EMPLOYEE-OWNED · NORTHEAST WISCONSIN</t>
+          <t>EMPLOYEE-OWNED · NORTHEAST WISCONSIN · SINCE 1946</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -812,7 +963,11 @@
           <t>We'll only use your email to send your results.</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>To access or remove your information, contact your local WG&amp;R store.</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>In stock at WG&amp;R</t>
@@ -863,7 +1018,11 @@
           <t>Solo usaremos tu correo para enviarte tus resultados.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Para acceder o eliminar tu información, comunícate con tu tienda WG&amp;R local.</t>
+        </is>
+      </c>
       <c r="AG2" t="inlineStr">
         <is>
           <t>En stock en WG&amp;R</t>
@@ -878,42 +1037,34 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>WG&amp;R Sleep Consultation</t>
+          <t>EMPLOYEE-OWNED · NORTHEAST WISCONSIN · SINCE 1946</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Let's find the mattress</t>
+          <t>Northeast Wisconsin’s</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>made for how you sleep</t>
+          <t>Sleep Shop.</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer a few questions and our sleep specialists will match you to the right mattress — proudly </t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>employee-owned in Northeast Wisconsin since 1946</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
+          <t>Answer a few questions, then review your mattress matches with a WG&amp;R sleep specialist.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Start My Sleep Consultation</t>
+          <t>Find My Sleep Match</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>About 2 minutes, no pressure</t>
+          <t>About 2 minutes · No pressure</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -950,35 +1101,173 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
+          <t>illustrative</t>
+        </is>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>a qualifying DreamFinder mattress selection</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>una selección de colchón DreamFinder que califique</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>A 30-day offer to bring home with your matches</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Una oferta de 30 días para llevar con tus recomendaciones</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Live delivery can be connected after WG&amp;R approves the experience.</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>La entrega real se puede conectar después de que WG&amp;R apruebe la experiencia.</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Valid on qualifying mattress selections. Cannot be combined with other offers. Final eligibility confirmed by your WG&amp;R sleep specialist.</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Válido en selecciones de colchones que califiquen. No se puede combinar con otras ofertas. Elegibilidad final confirmada por tu especialista de sueño de WG&amp;R.</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Draft policy — pending WG&amp;R approval before live use.</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>DreamFinder collects your name, email, and optional phone number to deliver your mattress recommendations and Savings Pass. Your information is only used for this purpose and is never sold or shared with third parties.</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>Disclaimer</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>DreamFinder is a product recommendation tool. Match percentages and Sleep Brief guidance are generated from your quiz answers and should be treated as starting points, not guarantees. This tool does not provide medical advice — consult a healthcare provider for medical sleep concerns. Discounts and product availability are subject to WG&amp;R store terms.</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>Green Bay · Appleton · Oshkosh · Sheboygan · Manitowoc · Fond du Lac</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Política preliminar — pendiente de aprobación de WG&amp;R antes de su uso.</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>DreamFinder recopila tu nombre, correo electrónico y número de teléfono opcional para enviarte tus recomendaciones de colchón y tu Pase de Ahorro. Tu información se usa únicamente para este fin y nunca se vende ni se comparte con terceros.</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>Aviso legal</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>DreamFinder es una herramienta de recomendación de productos. Los porcentajes de compatibilidad y la guía del Resumen de Sueño se generan a partir de tus respuestas y deben tomarse como punto de partida, no como garantía. Esta herramienta no ofrece asesoramiento médico — consulta a un profesional de la salud para problemas médicos del sueño. Los descuentos y la disponibilidad de productos están sujetos a los términos de las tiendas WG&amp;R.</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>SLEEP SHOP</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>Your consultation builds</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>Sleep Brief · Mattress Matches · Sleep System Picks · Savings Pass</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>TIENDA DEL DESCANSO</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>Tu consulta crea</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>Resumen de Sueño · Opciones de Colchón · Sistema de Sueño · Pase de Ahorro</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>DreamFinder - WG&amp;R Furniture</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>DreamFinder</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>Personalized sleep consultation for WG&amp;R Furniture</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>/WGRFurniture/</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>#0f1f33</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>#0f1f33</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6740,4 +7029,32 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Promotions JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"activeScenario": "memorial-day-2026-demo", "timeZone": "America/Chicago", "scenarios": {"current": {"kind": "current", "demoOnly": false, "checkedAt": "2026-06-08", "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "sourceNote": {"en": "Offers reflect WG&amp;R's official website and are confirmed by your WG&amp;R sleep specialist.", "es": "Las ofertas reflejan el sitio web oficial de WG&amp;R y las confirma tu especialista de sueño de WG&amp;R."}, "items": [{"id": "tempurpedic-offer", "verified": true, "type": "offer", "eligibleBrands": ["Tempur-Pedic"], "eligibleMattressIds": [], "badge": {"en": "Current WG&amp;R Offer", "es": "Oferta actual de WG&amp;R"}, "headline": {"en": "Tempur-Pedic: free delivery, up to 5-year financing, and a $300 Mastercard® Rewards Card", "es": "Tempur-Pedic: entrega gratis, financiamiento hasta 5 años y una tarjeta Mastercard® de $300 en recompensas"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop page. Offer details and current availability confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en la página Sleep Shop de WG&amp;R. Tu especialista de sueño de WG&amp;R confirma los detalles y la disponibilidad actual."}, "disclosure": {"en": "Financing subject to credit approval. May not combine with the Savings Pass or percentage-off offers — ask your WG&amp;R specialist.", "es": "Financiamiento sujeto a aprobación de crédito. Puede no combinarse con el Pase de Ahorro ni con ofertas de porcentaje de descuento — pregunta a tu especialista de WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sleep-shop", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "tempurpedic-125night-guarantee", "verified": true, "type": "guarantee", "eligibleBrands": ["Tempur-Pedic"], "eligibleMattressIds": [], "badge": {"en": "125-Night Guarantee", "es": "Garantía de 125 noches"}, "headline": {"en": "125-night sleep satisfaction guarantee", "es": "Garantía de satisfacción de sueño de 125 noches"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop page. Terms confirmed by your WG&amp;R sleep specialist.", "es": "Mostrada en la página Sleep Shop de WG&amp;R. Tu especialista de sueño de WG&amp;R confirma los términos."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sleep-shop", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "wgr-financing", "verified": true, "type": "financing", "badge": {"en": "Financing Available", "es": "Financiamiento disponible"}, "headline": {"en": "0% APR financing available (12, 36, or 60 months)", "es": "Financiamiento con 0% APR disponible (12, 36 o 60 meses)"}, "detail": {"en": "Subject to credit approval. Not valid on power buys, floor samples, or clearance. Cannot combine with percentage-off discounts or gift-with-purchase. Ask your WG&amp;R specialist.", "es": "Sujeto a aprobación de crédito. No válido en power buys, muestras de piso ni liquidación. No se combina con descuentos de porcentaje ni regalo con compra. Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "New accounts as of 7/31/2025: Purchase APR 34.99%, Penalty APR 39.99%, Minimum Interest Charge $2. Subject to credit approval.", "es": "Cuentas nuevas desde el 31/7/2025: APR de compra 34.99%, APR de penalización 39.99%, cargo mínimo de interés $2. Sujeto a aprobación de crédito."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/financing", "checkedAt": "2026-06-08", "savingsPassPolicy": "alternative"}, {"id": "wgr-delivery-49", "verified": true, "type": "service", "badge": {"en": "Delivery from $49", "es": "Entrega desde $49"}, "headline": {"en": "Delivery starting at $49", "es": "Entrega desde $49"}, "detail": {"en": "Starting prices reflect WG&amp;R's standard delivery area. Exclusions apply (clearance, closeouts, floor samples, doorbusters, and select brands including Tempur-Pedic, Purple, and Casper). Ask your WG&amp;R specialist.", "es": "Los precios iniciales reflejan el área de entrega estándar de WG&amp;R. Aplican exclusiones (liquidación, cierres, muestras de piso, ofertas especiales y ciertas marcas como Tempur-Pedic, Purple y Casper). Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-more-offers", "verified": true, "type": "pointer", "badge": {"en": "More Current Offers", "es": "Más ofertas actuales"}, "headline": {"en": "WG&amp;R runs additional current offers (Power Buys, brand deals, clearance)", "es": "WG&amp;R tiene ofertas actuales adicionales (Power Buys, ofertas de marca, liquidación)"}, "detail": {"en": "Some offers appear only on WG&amp;R's promotions pages. Ask your WG&amp;R specialist for current details.", "es": "Algunas ofertas solo aparecen en las páginas de promociones de WG&amp;R. Pregunta a tu especialista de WG&amp;R por los detalles actuales."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}]}, "memorial-day-2026-demo": {"kind": "historical-demo", "period": {"startsAt": "2026-05-05", "endsAt": "2026-06-02", "timeZone": "America/Chicago"}, "disclosure": {"en": "Historical Demo · Pre–Memorial Day 2026 — Offers shown are a reconstruction of promotions advertised during May 2026 and are not current offers.", "es": "Demostración histórica · Antes del Día de los Caídos de 2026 — Las ofertas mostradas reconstruyen promociones anunciadas durante mayo de 2026 y no son ofertas actuales."}, "disableEmailSubmission": true, "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "items": [{"id": "md2026-purple-rejuvenate", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["g7"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $500 savings", "es": "Ahorro de $500 observado anteriormente"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-rejuvenate-twin-xl-mattress/3020940/3017912", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-restore-firm", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s2"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $250 savings (Twin XL, as observed)", "es": "Ahorro de $250 observado anteriormente (Twin XL, según lo observado)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-restore-firm-twin-xl-mattress/2954265/2916623", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-mattress", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s1"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed promotional pricing varying by size", "es": "Precio promocional observado anteriormente, variable según el tamaño"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "md2026-storewide-20", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "type": "reconstructed-storewide", "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Event", "es": "Evento histórico reconstruido"}, "headline": {"en": "Previously observed 20% off during Memorial Day sale (storewide)", "es": "20% de descuento durante la venta del Día de los Caídos, observado anteriormente (en toda la tienda)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Applied to no individual product without WG&amp;R product-specific evidence.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. No se aplica a ningún producto individual sin evidencia específica de producto de WG&amp;R."}, "disclosure": {"en": "Recorded exclusions: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, select Sealy, Beautyrest Black Hybrid, Power Buys, clearance.", "es": "Exclusiones registradas: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, ciertos Sealy, Beautyrest Black Hybrid, Power Buys, liquidación."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "savingsPassPolicy": "specialist_confirm"}]}}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/incoming/WGR_Store_Data.xlsx
+++ b/incoming/WGR_Store_Data.xlsx
@@ -7050,7 +7050,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"activeScenario": "memorial-day-2026-demo", "timeZone": "America/Chicago", "scenarios": {"current": {"kind": "current", "demoOnly": false, "checkedAt": "2026-06-08", "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "sourceNote": {"en": "Offers reflect WG&amp;R's official website and are confirmed by your WG&amp;R sleep specialist.", "es": "Las ofertas reflejan el sitio web oficial de WG&amp;R y las confirma tu especialista de sueño de WG&amp;R."}, "items": [{"id": "tempurpedic-offer", "verified": true, "type": "offer", "eligibleBrands": ["Tempur-Pedic"], "eligibleMattressIds": [], "badge": {"en": "Current WG&amp;R Offer", "es": "Oferta actual de WG&amp;R"}, "headline": {"en": "Tempur-Pedic: free delivery, up to 5-year financing, and a $300 Mastercard® Rewards Card", "es": "Tempur-Pedic: entrega gratis, financiamiento hasta 5 años y una tarjeta Mastercard® de $300 en recompensas"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop page. Offer details and current availability confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en la página Sleep Shop de WG&amp;R. Tu especialista de sueño de WG&amp;R confirma los detalles y la disponibilidad actual."}, "disclosure": {"en": "Financing subject to credit approval. May not combine with the Savings Pass or percentage-off offers — ask your WG&amp;R specialist.", "es": "Financiamiento sujeto a aprobación de crédito. Puede no combinarse con el Pase de Ahorro ni con ofertas de porcentaje de descuento — pregunta a tu especialista de WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sleep-shop", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "tempurpedic-125night-guarantee", "verified": true, "type": "guarantee", "eligibleBrands": ["Tempur-Pedic"], "eligibleMattressIds": [], "badge": {"en": "125-Night Guarantee", "es": "Garantía de 125 noches"}, "headline": {"en": "125-night sleep satisfaction guarantee", "es": "Garantía de satisfacción de sueño de 125 noches"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop page. Terms confirmed by your WG&amp;R sleep specialist.", "es": "Mostrada en la página Sleep Shop de WG&amp;R. Tu especialista de sueño de WG&amp;R confirma los términos."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sleep-shop", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "wgr-financing", "verified": true, "type": "financing", "badge": {"en": "Financing Available", "es": "Financiamiento disponible"}, "headline": {"en": "0% APR financing available (12, 36, or 60 months)", "es": "Financiamiento con 0% APR disponible (12, 36 o 60 meses)"}, "detail": {"en": "Subject to credit approval. Not valid on power buys, floor samples, or clearance. Cannot combine with percentage-off discounts or gift-with-purchase. Ask your WG&amp;R specialist.", "es": "Sujeto a aprobación de crédito. No válido en power buys, muestras de piso ni liquidación. No se combina con descuentos de porcentaje ni regalo con compra. Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "New accounts as of 7/31/2025: Purchase APR 34.99%, Penalty APR 39.99%, Minimum Interest Charge $2. Subject to credit approval.", "es": "Cuentas nuevas desde el 31/7/2025: APR de compra 34.99%, APR de penalización 39.99%, cargo mínimo de interés $2. Sujeto a aprobación de crédito."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/financing", "checkedAt": "2026-06-08", "savingsPassPolicy": "alternative"}, {"id": "wgr-delivery-49", "verified": true, "type": "service", "badge": {"en": "Delivery from $49", "es": "Entrega desde $49"}, "headline": {"en": "Delivery starting at $49", "es": "Entrega desde $49"}, "detail": {"en": "Starting prices reflect WG&amp;R's standard delivery area. Exclusions apply (clearance, closeouts, floor samples, doorbusters, and select brands including Tempur-Pedic, Purple, and Casper). Ask your WG&amp;R specialist.", "es": "Los precios iniciales reflejan el área de entrega estándar de WG&amp;R. Aplican exclusiones (liquidación, cierres, muestras de piso, ofertas especiales y ciertas marcas como Tempur-Pedic, Purple y Casper). Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-more-offers", "verified": true, "type": "pointer", "badge": {"en": "More Current Offers", "es": "Más ofertas actuales"}, "headline": {"en": "WG&amp;R runs additional current offers (Power Buys, brand deals, clearance)", "es": "WG&amp;R tiene ofertas actuales adicionales (Power Buys, ofertas de marca, liquidación)"}, "detail": {"en": "Some offers appear only on WG&amp;R's promotions pages. Ask your WG&amp;R specialist for current details.", "es": "Algunas ofertas solo aparecen en las páginas de promociones de WG&amp;R. Pregunta a tu especialista de WG&amp;R por los detalles actuales."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}]}, "memorial-day-2026-demo": {"kind": "historical-demo", "period": {"startsAt": "2026-05-05", "endsAt": "2026-06-02", "timeZone": "America/Chicago"}, "disclosure": {"en": "Historical Demo · Pre–Memorial Day 2026 — Offers shown are a reconstruction of promotions advertised during May 2026 and are not current offers.", "es": "Demostración histórica · Antes del Día de los Caídos de 2026 — Las ofertas mostradas reconstruyen promociones anunciadas durante mayo de 2026 y no son ofertas actuales."}, "disableEmailSubmission": true, "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "items": [{"id": "md2026-purple-rejuvenate", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["g7"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $500 savings", "es": "Ahorro de $500 observado anteriormente"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-rejuvenate-twin-xl-mattress/3020940/3017912", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-restore-firm", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s2"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $250 savings (Twin XL, as observed)", "es": "Ahorro de $250 observado anteriormente (Twin XL, según lo observado)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-restore-firm-twin-xl-mattress/2954265/2916623", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-mattress", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s1"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed promotional pricing varying by size", "es": "Precio promocional observado anteriormente, variable según el tamaño"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "md2026-storewide-20", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "type": "reconstructed-storewide", "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Event", "es": "Evento histórico reconstruido"}, "headline": {"en": "Previously observed 20% off during Memorial Day sale (storewide)", "es": "20% de descuento durante la venta del Día de los Caídos, observado anteriormente (en toda la tienda)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Applied to no individual product without WG&amp;R product-specific evidence.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. No se aplica a ningún producto individual sin evidencia específica de producto de WG&amp;R."}, "disclosure": {"en": "Recorded exclusions: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, select Sealy, Beautyrest Black Hybrid, Power Buys, clearance.", "es": "Exclusiones registradas: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, ciertos Sealy, Beautyrest Black Hybrid, Power Buys, liquidación."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "savingsPassPolicy": "specialist_confirm"}]}}}</t>
+          <t>{"activeScenario": "current", "timeZone": "America/Chicago", "scenarios": {"current": {"kind": "current", "demoOnly": false, "checkedAt": "2026-06-08", "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "sourceNote": {"en": "Offers reflect WG&amp;R's official website and are confirmed by your WG&amp;R sleep specialist.", "es": "Las ofertas reflejan el sitio web oficial de WG&amp;R y las confirma tu especialista de sueño de WG&amp;R."}, "items": [{"id": "wgr-tempurpedic-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["g1", "g2", "g3"], "badge": {"en": "Free Delivery + $300 Card", "es": "Entrega gratis + tarjeta de $300"}, "headline": {"en": "Free Delivery + Free $300 Mastercard® Rewards Card to spend anywhere†", "es": "Entrega gratis + tarjeta Mastercard® de $300 en recompensas para gastar donde quieras†"}, "detail": {"en": "Includes special financing. Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Incluye financiamiento especial. Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "See WG&amp;R for offer terms.", "es": "Consulta los términos de la oferta en WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/tempurpedic", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-sealy-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["s5", "s6", "b4"], "badge": {"en": "Free $200 Gift", "es": "Regalo gratis de $200"}, "headline": {"en": "Free $200 Gift∞ to spend on accessories", "es": "Regalo gratis de $200∞ para gastar en accesorios"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "See WG&amp;R for offer terms.", "es": "Consulta los términos de la oferta en WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sealy", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-stearns-foster-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["g4", "g5"], "badge": {"en": "Free Delivery + $300 Card", "es": "Entrega gratis + tarjeta de $300"}, "headline": {"en": "FREE DELIVERY + FREE $300 Mastercard® Rewards Card to spend anywhere†", "es": "ENTREGA GRATIS + tarjeta Mastercard® de $300 en recompensas para gastar donde quieras†"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "See WG&amp;R for offer terms.", "es": "Consulta los términos de la oferta en WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/stearns-foster", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-beautyrest-black-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["g8", "s7"], "badge": {"en": "Free Adjustable Base", "es": "Base ajustable gratis"}, "headline": {"en": "Free baselogic™ Silver adjustable base with purchase (up to a $599 value) — limited time only, ends 6/16", "es": "Base ajustable baselogic™ Silver gratis con tu compra (hasta $599 de valor) — por tiempo limitado, termina el 6/16"}, "detail": {"en": "Free delivery included. Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Incluye entrega gratis. Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "endsAt": "2026-06-16T23:59:59-05:00", "expiration": "June 16, 2026", "sourceUrl": "https://www.wgrfurniture.com/beautyrest-black", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-purple-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["g7", "s1", "s2"], "badge": {"en": "Free Delivery + Gift", "es": "Entrega gratis + regalo"}, "headline": {"en": "Free Delivery + Free Gift With Purchase, up to $300 value∞", "es": "Entrega gratis + regalo gratis con tu compra, hasta $300 de valor∞"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "See WG&amp;R for offer terms.", "es": "Consulta los términos de la oferta en WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/purple", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-smartlife-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["g9"], "badge": {"en": "Free Delivery", "es": "Entrega gratis"}, "headline": {"en": "Free Delivery", "es": "Entrega gratis"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/search/mattresses/shop-by-brand/smartlife", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-nectar-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["s10", "b1", "b2"], "badge": {"en": "Free Delivery", "es": "Entrega gratis"}, "headline": {"en": "Free Delivery", "es": "Entrega gratis"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/search/mattresses/shop-by-brand/nectar", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-casper-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["s3", "s4"], "badge": {"en": "Free Delivery", "es": "Entrega gratis"}, "headline": {"en": "Free Delivery", "es": "Entrega gratis"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/casper", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-dreamcloud-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["b3", "b7"], "badge": {"en": "Free Delivery", "es": "Entrega gratis"}, "headline": {"en": "Free Delivery", "es": "Entrega gratis"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/search/mattresses/shop-by-brand/dreamcloud", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-astor-park-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["s8", "s9"], "badge": {"en": "Save 20%", "es": "Ahorra 20%"}, "headline": {"en": "Limited time only — Save 20% on mattresses", "es": "Por tiempo limitado — Ahorra 20% en colchones"}, "detail": {"en": "Hand-crafted in Two Rivers. Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Hecho a mano en Two Rivers. Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/search/mattresses/shop-by-brand/astor-park", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}, {"id": "wgr-factory-direct-offer", "verified": true, "type": "offer", "evidenceStatus": "wgr-current-page", "eligibleBrands": [], "eligibleMattressIds": ["b5"], "badge": {"en": "Save 20%", "es": "Ahorra 20%"}, "headline": {"en": "Limited time only — Save 20% on mattresses^", "es": "Por tiempo limitado — Ahorra 20% en colchones^"}, "detail": {"en": "Hand-crafted in Two Rivers. Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist. May not combine with the Savings Pass or other offers — ask your WG&amp;R specialist.", "es": "Hecho a mano en Two Rivers. Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R. Puede no combinarse con el Pase de Ahorro ni con otras ofertas — pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "See WG&amp;R for offer terms.", "es": "Consulta los términos de la oferta en WG&amp;R."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/factory-direct", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "wgr-financing", "verified": true, "type": "financing", "badge": {"en": "Financing Available", "es": "Financiamiento disponible"}, "headline": {"en": "0% APR financing available (12, 36, or 60 months)", "es": "Financiamiento con 0% APR disponible (12, 36 o 60 meses)"}, "detail": {"en": "Subject to credit approval. Not valid on power buys, floor samples, or clearance. Cannot combine with percentage-off discounts or gift-with-purchase. Ask your WG&amp;R specialist.", "es": "Sujeto a aprobación de crédito. No válido en power buys, muestras de piso ni liquidación. No se combina con descuentos de porcentaje ni regalo con compra. Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "New accounts as of 7/31/2025: Purchase APR 34.99%, Penalty APR 39.99%, Minimum Interest Charge $2. Subject to credit approval.", "es": "Cuentas nuevas desde el 31/7/2025: APR de compra 34.99%, APR de penalización 39.99%, cargo mínimo de interés $2. Sujeto a aprobación de crédito."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/financing", "checkedAt": "2026-06-08", "savingsPassPolicy": "alternative"}, {"id": "wgr-125night-guarantee", "verified": true, "type": "guarantee", "evidenceStatus": "wgr-current-page", "badge": {"en": "125-Night Guarantee", "es": "Garantía de 125 noches"}, "headline": {"en": "125 sleep satisfaction guarantee", "es": "Garantía de satisfacción de sueño de 125 noches"}, "detail": {"en": "Shown on WG&amp;R's Sleep Shop; confirmed by your WG&amp;R sleep specialist.", "es": "Mostrado en el Sleep Shop de WG&amp;R; lo confirma tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/sleep-shop", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-delivery-49", "verified": true, "type": "service", "badge": {"en": "Delivery from $49", "es": "Entrega desde $49"}, "headline": {"en": "Delivery starting at $49", "es": "Entrega desde $49"}, "detail": {"en": "Starting prices reflect WG&amp;R's standard delivery area. Exclusions apply (clearance, closeouts, floor samples, doorbusters, and select brands including Tempur-Pedic, Purple, and Casper). Ask your WG&amp;R specialist.", "es": "Los precios iniciales reflejan el área de entrega estándar de WG&amp;R. Aplican exclusiones (liquidación, cierres, muestras de piso, ofertas especiales y ciertas marcas como Tempur-Pedic, Purple y Casper). Pregunta a tu especialista de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "stackable"}, {"id": "wgr-more-offers", "verified": true, "type": "pointer", "badge": {"en": "More Current Offers", "es": "Más ofertas actuales"}, "headline": {"en": "WG&amp;R runs additional current offers (Power Buys, brand deals, clearance)", "es": "WG&amp;R tiene ofertas actuales adicionales (Power Buys, ofertas de marca, liquidación)"}, "detail": {"en": "Some offers appear only on WG&amp;R's promotions pages. Ask your WG&amp;R specialist for current details.", "es": "Algunas ofertas solo aparecen en las páginas de promociones de WG&amp;R. Pregunta a tu especialista de WG&amp;R por los detalles actuales."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "checkedAt": "2026-06-08", "savingsPassPolicy": "specialist_confirm"}]}, "memorial-day-2026-demo": {"kind": "historical-demo", "period": {"startsAt": "2026-05-05", "endsAt": "2026-06-02", "timeZone": "America/Chicago"}, "disclosure": {"en": "Historical Demo · Pre–Memorial Day 2026 — Offers shown are a reconstruction of promotions advertised during May 2026 and are not current offers.", "es": "Demostración histórica · Antes del Día de los Caídos de 2026 — Las ofertas mostradas reconstruyen promociones anunciadas durante mayo de 2026 y no son ofertas actuales."}, "disableEmailSubmission": true, "spanishStatus": "draft", "spanishDraftNote": {"en": "", "es": "Traducción preliminar — confirma los detalles con tu especialista de WG&amp;R."}, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "items": [{"id": "md2026-purple-rejuvenate", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["g7"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $500 savings", "es": "Ahorro de $500 observado anteriormente"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-rejuvenate-twin-xl-mattress/3020940/3017912", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-restore-firm", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s2"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed $250 savings (Twin XL, as observed)", "es": "Ahorro de $250 observado anteriormente (Twin XL, según lo observado)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/product/group/mattresses/shop-by-size/twin-xl/purp/purple-restore-firm-twin-xl-mattress/2954265/2916623", "savingsPassPolicy": "specialist_confirm"}, {"id": "md2026-purple-mattress", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "eligibleMattressIds": ["s1"], "eligibleAccessoryIds": [], "eligibleBrands": [], "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Offer", "es": "Oferta histórica reconstruida"}, "headline": {"en": "Previously observed promotional pricing varying by size", "es": "Precio promocional observado anteriormente, variable según el tamaño"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Confirm with your WG&amp;R sleep specialist.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. Confírmalo con tu especialista de sueño de WG&amp;R."}, "disclosure": {"en": "", "es": ""}, "expiration": "not shown", "sourceUrl": "", "savingsPassPolicy": "specialist_confirm"}], "storewide": [{"id": "md2026-storewide-20", "reconstructedHistorical": true, "evidenceStatus": "prior-research-observation", "evidenceProvenance": {"en": "Previously observed on a WG&amp;R-indexed or WG&amp;R product result, but not independently retrievable as of 2026-06-08.", "es": "Observado anteriormente en un resultado indexado de WG&amp;R o en una página de producto de WG&amp;R, pero no recuperable de forma independiente al 2026-06-08."}, "type": "reconstructed-storewide", "eligibleForStorewide20": false, "badge": {"en": "Reconstructed Historical Event", "es": "Evento histórico reconstruido"}, "headline": {"en": "Previously observed 20% off during Memorial Day sale (storewide)", "es": "20% de descuento durante la venta del Día de los Caídos, observado anteriormente (en toda la tienda)"}, "detail": {"en": "Reconstructed from prior research; not a current offer. Applied to no individual product without WG&amp;R product-specific evidence.", "es": "Reconstruido a partir de investigación previa; no es una oferta actual. No se aplica a ningún producto individual sin evidencia específica de producto de WG&amp;R."}, "disclosure": {"en": "Recorded exclusions: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, select Sealy, Beautyrest Black Hybrid, Power Buys, clearance.", "es": "Exclusiones registradas: Tempur-Pedic, Purple, Casper, Nectar, DreamCloud, Stearns &amp; Foster, ciertos Sealy, Beautyrest Black Hybrid, Power Buys, liquidación."}, "expiration": "not shown", "sourceUrl": "https://www.wgrfurniture.com/current-promotions", "savingsPassPolicy": "specialist_confirm"}]}}}</t>
         </is>
       </c>
     </row>
